--- a/Trắc nghiệm ôn luyện/BA Functional/multiple_choice_sample_template_BA_FRAMEWORKS.xlsx
+++ b/Trắc nghiệm ôn luyện/BA Functional/multiple_choice_sample_template_BA_FRAMEWORKS.xlsx
@@ -453,19 +453,19 @@
         <v>SWOT là viết tắt của Strengths (Điểm mạnh), Weaknesses (Điểm yếu), Opportunities (Cơ hội), và Threats (Thách thức). Weaknesses là yếu tố nội bộ tiêu cực.</v>
       </c>
       <c r="E2" t="str">
-        <v>Weaknesses — Điểm yếu nội tại của doanh nghiệp hoặc sản phẩm cần khắc phục — yếu tố nội bộ tiêu cực</v>
+        <v>Websites — Hệ thống trang thông tin điện tử của doanh nghiệp — yếu tố kỹ thuật</v>
       </c>
       <c r="F2" t="str">
-        <v>Websites — Hệ thống trang thông tin điện tử của doanh nghiệp — yếu tố kỹ thuật</v>
+        <v>Wants — Những mong muốn chủ quan của ban giám đốc dự án — yếu tố mong muốn</v>
       </c>
       <c r="G2" t="str">
         <v>Workflows — Quy trình làm việc giữa các phòng ban trong công ty — quy trình vận hành</v>
       </c>
       <c r="H2" t="str">
-        <v>Wants — Những mong muốn chủ quan của ban giám đốc dự án — yếu tố mong muốn</v>
+        <v>Weaknesses — Điểm yếu nội tại của doanh nghiệp hoặc sản phẩm cần khắc phục — yếu tố nội bộ tiêu cực</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -482,19 +482,19 @@
         <v>PESTEL là công cụ phân tích các yếu tố vĩ mô bao gồm: Political (Chính trị), Economic (Kinh tế), Social (Xã hội), Technological (Công nghệ), Environmental (Môi trường), Legal (Pháp lý).</v>
       </c>
       <c r="E3" t="str">
-        <v>Các yếu tố vĩ mô ngoài tầm kiểm soát của doanh nghiệp ảnh hưởng đến môi trường kinh doanh — môi trường vĩ mô</v>
+        <v>Cấu trúc bảng và các mối quan hệ kho dữ liệu SQL của dự án — kỹ thuật database</v>
       </c>
       <c r="F3" t="str">
         <v>Năng suất làm việc hàng ngày của từng lập trình viên trong team — năng suất nội bộ</v>
       </c>
       <c r="G3" t="str">
-        <v>Cấu trúc bảng và các mối quan hệ kho dữ liệu SQL của dự án — kỹ thuật database</v>
+        <v>Các kịch bản kiểm thử bảo mật cho cổng thanh toán trực tuyến — bảo mật hệ thống</v>
       </c>
       <c r="H3" t="str">
-        <v>Các kịch bản kiểm thử bảo mật cho cổng thanh toán trực tuyến — bảo mật hệ thống</v>
+        <v>Các yếu tố vĩ mô ngoài tầm kiểm soát của doanh nghiệp ảnh hưởng đến môi trường kinh doanh — môi trường vĩ mô</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -511,19 +511,19 @@
         <v>Value Propositions (Tuyên bố giá trị) là lý do vì sao khách hàng chọn sản phẩm của bạn thay vì đối thủ. Nó giải quyết vấn đề hoặc đáp ứng nhu cầu cụ thể của khách hàng.</v>
       </c>
       <c r="E4" t="str">
+        <v>Tổng chi phí ước tính để duy trì hoạt động của máy chủ Cloud trong một năm — chi phí hạ tầng</v>
+      </c>
+      <c r="F4" t="str">
         <v>Tuyên bố giá trị độc đáo mà sản phẩm/dịch vụ mang lại để giải quyết nỗi đau của khách hàng — giá trị cốt lõi</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
+        <v>Các kênh truyền thông quảng cáo trực tuyến để tiếp cận người dùng — kênh tiếp thị</v>
+      </c>
+      <c r="H4" t="str">
         <v>Danh sách các đối thủ cạnh tranh trực tiếp trên thị trường — đối thủ cạnh tranh</v>
       </c>
-      <c r="G4" t="str">
-        <v>Tổng chi phí ước tính để duy trì hoạt động của máy chủ Cloud trong một năm — chi phí hạ tầng</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Các kênh truyền thông quảng cáo trực tuyến để tiếp cận người dùng — kênh tiếp thị</v>
-      </c>
       <c r="I4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -540,7 +540,7 @@
         <v>Stakeholder (Bên liên quan) là mọi đối tượng có lợi ích, quyền lợi hoặc chịu tác động từ sự thành bại của dự án phần mềm.</v>
       </c>
       <c r="E5" t="str">
-        <v>Bất kỳ cá nhân hoặc tổ chức nào có ảnh hưởng hoặc chịu ảnh hưởng bởi quyết định/kết quả của dự án — bên liên quan</v>
+        <v>Những khách hàng đã mua sản phẩm và đánh giá 5 sao trên ứng dụng di động — khách hàng trung thành</v>
       </c>
       <c r="F5" t="str">
         <v>Chỉ duy nhất người đại diện ký hợp đồng thanh toán chi phí cho dự án — nhà tài trợ</v>
@@ -549,10 +549,10 @@
         <v>Lập trình viên chịu trách nhiệm viết tài liệu thiết kế hệ thống — kỹ sư hệ thống</v>
       </c>
       <c r="H5" t="str">
-        <v>Những khách hàng đã mua sản phẩm và đánh giá 5 sao trên ứng dụng di động — khách hàng trung thành</v>
+        <v>Bất kỳ cá nhân hoặc tổ chức nào có ảnh hưởng hoặc chịu ảnh hưởng bởi quyết định/kết quả của dự án — bên liên quan</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -569,19 +569,19 @@
         <v>BABOK là bộ tiêu chuẩn thế giới về phân tích nghiệp vụ, được nghiên cứu và phát triển bởi tổ chức phi lợi nhuận IIBA.</v>
       </c>
       <c r="E6" t="str">
+        <v>W3C (World Wide Web Consortium) — Tổ chức định chuẩn Web quốc tế</v>
+      </c>
+      <c r="F6" t="str">
         <v>IIBA (International Institute of Business Analysis) — Viện Phân tích Nghiệp vụ Quốc tế</v>
       </c>
-      <c r="F6" t="str">
+      <c r="G6" t="str">
         <v>PMI (Project Management Institute) — Viện Quản lý Dự án Hoa Kỳ</v>
       </c>
-      <c r="G6" t="str">
+      <c r="H6" t="str">
         <v>IEEE (Institute of Electrical and Electronics Engineers) — Viện Kỹ sư Điện và Điện tử</v>
       </c>
-      <c r="H6" t="str">
-        <v>W3C (World Wide Web Consortium) — Tổ chức định chuẩn Web quốc tế</v>
-      </c>
       <c r="I6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -598,19 +598,19 @@
         <v>RACI là viết tắt của: Responsible (Người thực hiện), Accountable (Người phê duyệt/Giải trình tối cao), Consulted (Người tham vấn), Informed (Người nhận thông tin). Chỉ có duy nhất 1 chữ "A" cho mỗi đầu việc.</v>
       </c>
       <c r="E7" t="str">
+        <v>Approved — Khách hàng đã ký biên bản nghiệm thu bàn giao sản phẩm — phê duyệt nghiệm thu</v>
+      </c>
+      <c r="F7" t="str">
         <v>Accountable — Người chịu trách nhiệm phê duyệt cuối cùng và sở hữu kết quả công việc — người chịu trách nhiệm tối cao</v>
       </c>
-      <c r="F7" t="str">
+      <c r="G7" t="str">
+        <v>Analyst — Business Analyst chịu trách nhiệm viết tài liệu mô tả yêu cầu — nhà phân tích</v>
+      </c>
+      <c r="H7" t="str">
         <v>Assigned — Lập trình viên được phân công trực tiếp vào code chức năng đó — người thực hiện</v>
       </c>
-      <c r="G7" t="str">
-        <v>Approved — Khách hàng đã ký biên bản nghiệm thu bàn giao sản phẩm — phê duyệt nghiệm thu</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Analyst — Business Analyst chịu trách nhiệm viết tài liệu mô tả yêu cầu — nhà phân tích</v>
-      </c>
       <c r="I7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -627,19 +627,19 @@
         <v>Porter's Five Forces phân tích 5 áp lực: Đối thủ cạnh tranh ngành, Quyền lực nhà cung cấp, Quyền lực người mua, Đe dọa từ sản phẩm thay thế, và Đe dọa từ đối thủ mới.</v>
       </c>
       <c r="E8" t="str">
+        <v>Kế hoạch phân chia ca làm việc cho nhân sự trực tổng đài hỗ trợ khách hàng — phân ca làm việc</v>
+      </c>
+      <c r="F8" t="str">
         <v>Mức độ cạnh tranh và tính hấp dẫn về mặt lợi nhuận của một ngành công nghiệp — phân tích cấu trúc ngành</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Số lượng lỗi tối đa mà hệ thống phần mềm có thể chấp nhận trước khi sập — giới hạn lỗi kỹ thuật</v>
       </c>
       <c r="G8" t="str">
         <v>Các công nghệ lập trình Frontend phổ biến nhất trong năm hiện tại — xu hướng kỹ thuật</v>
       </c>
       <c r="H8" t="str">
-        <v>Kế hoạch phân chia ca làm việc cho nhân sự trực tổng đài hỗ trợ khách hàng — phân ca làm việc</v>
+        <v>Số lượng lỗi tối đa mà hệ thống phần mềm có thể chấp nhận trước khi sập — giới hạn lỗi kỹ thuật</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -656,19 +656,19 @@
         <v>Strengths và Weaknesses là các yếu tố nội bộ (Internal). Opportunities và Threats là các yếu tố thuộc môi trường bên ngoài (External).</v>
       </c>
       <c r="E9" t="str">
+        <v>Quy định về thời gian làm việc hành chính của nhân viên trong công ty — quy định hành chính</v>
+      </c>
+      <c r="F9" t="str">
         <v>Môi trường bên ngoài doanh nghiệp, doanh nghiệp không thể chủ động kiểm soát hoàn toàn — yếu tố ngoại cảnh</v>
       </c>
-      <c r="F9" t="str">
+      <c r="G9" t="str">
         <v>Nội tại bên trong doanh nghiệp, do ban giám đốc tự quyết định và điều chỉnh — yếu tố nội bộ</v>
       </c>
-      <c r="G9" t="str">
+      <c r="H9" t="str">
         <v>Đội ngũ phát triển phần mềm và các công cụ lập trình đang sử dụng — yếu tố kỹ thuật</v>
       </c>
-      <c r="H9" t="str">
-        <v>Quy định về thời gian làm việc hành chính của nhân viên trong công ty — quy định hành chính</v>
-      </c>
       <c r="I9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -685,19 +685,19 @@
         <v>Sơ đồ Venn giúp BA trực quan hóa các tính năng trùng nhau giữa hệ thống cũ và mới, từ đó xác định rõ phạm vi (scope) chuyển đổi dữ liệu và phát triển tính năng mới.</v>
       </c>
       <c r="E10" t="str">
+        <v>Tổng chi phí bản quyền phần mềm phải trả cho hai nhà cung cấp khác nhau — so sánh chi phí</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Độ tuổi trung bình của tập người dùng sử dụng hai hệ thống này — so sánh nhân khẩu học</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Tốc độ tải dữ liệu trung bình giữa hai hệ thống trên cùng một cấu hình phần cứng — so sánh hiệu năng</v>
+      </c>
+      <c r="H10" t="str">
         <v>Sự giao thoa về tính năng để xác định phần nào cần giữ lại, phần nào cần loại bỏ và phần nào cần xây mới — so sánh tập hợp tính năng</v>
       </c>
-      <c r="F10" t="str">
-        <v>Tốc độ tải dữ liệu trung bình giữa hai hệ thống trên cùng một cấu hình phần cứng — so sánh hiệu năng</v>
-      </c>
-      <c r="G10" t="str">
-        <v>Tổng chi phí bản quyền phần mềm phải trả cho hai nhà cung cấp khác nhau — so sánh chi phí</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Độ tuổi trung bình của tập người dùng sử dụng hai hệ thống này — so sánh nhân khẩu học</v>
-      </c>
       <c r="I10">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -714,19 +714,19 @@
         <v>Mô hình Kano giúp đánh giá mức độ hài lòng của khách hàng đối với các tính năng. Tính năng "Must-be" là bắt buộc phải có; "Attractive" là tính năng gây bất ngờ, tạo lợi thế cạnh tranh.</v>
       </c>
       <c r="E11" t="str">
+        <v>Immediate, Short-term, Long-term, Future — phân loại tiến độ bàn giao</v>
+      </c>
+      <c r="F11" t="str">
         <v>Must-be (Cơ bản), One-dimensional (Hiệu năng), Attractive (Hấp dẫn), Indifferent (Thờ ơ), Reverse (Ngược chiều) — phân loại trải nghiệm người dùng</v>
-      </c>
-      <c r="F11" t="str">
-        <v>High, Medium, Low, Critical — phân loại mức độ nghiêm trọng của lỗi phần mềm</v>
       </c>
       <c r="G11" t="str">
         <v>Functional, Non-functional, Technical, Business — phân loại thuộc tính yêu cầu</v>
       </c>
       <c r="H11" t="str">
-        <v>Immediate, Short-term, Long-term, Future — phân loại tiến độ bàn giao</v>
+        <v>High, Medium, Low, Critical — phân loại mức độ nghiêm trọng của lỗi phần mềm</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -743,19 +743,19 @@
         <v>Ma trận Power-Interest chia stakeholders thành 4 nhóm: Quyền lực cao/Quan tâm cao (Key Players - cần quản lý chặt chẽ), Quyền lực cao/Quan tâm thấp (Keep Satisfied), Quyền lực thấp/Quan tâm cao (Keep Informed), Quyền lực thấp/Quan tâm thấp (Monitor).</v>
       </c>
       <c r="E12" t="str">
-        <v>Mức độ ảnh hưởng (Power/Influence) và Mức độ quan tâm (Interest) đối với dự án — ma trận Power-Interest</v>
+        <v>Độ tuổi trung bình (Age) và Vị trí địa lý nơi họ sinh sống (Location) — ma trận nhân khẩu học</v>
       </c>
       <c r="F12" t="str">
         <v>Năng lực kỹ thuật lập trình (Technical skill) và Số năm kinh nghiệm làm việc (Experience) — ma trận năng lực</v>
       </c>
       <c r="G12" t="str">
+        <v>Mức độ ảnh hưởng (Power/Influence) và Mức độ quan tâm (Interest) đối với dự án — ma trận Power-Interest</v>
+      </c>
+      <c r="H12" t="str">
         <v>Mức lương hàng tháng (Salary) và Số giờ làm việc cam kết trong dự án (Working hours) — ma trận chi phí</v>
       </c>
-      <c r="H12" t="str">
-        <v>Độ tuổi trung bình (Age) và Vị trí địa lý nơi họ sinh sống (Location) — ma trận nhân khẩu học</v>
-      </c>
       <c r="I12">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -772,19 +772,19 @@
         <v>Biểu đồ xương cá phân nhóm nguyên nhân thành các loại (Con người, Quy trình, Máy móc...). Tại mỗi nhánh nguyên nhân, BA áp dụng câu hỏi 5 Why để đào sâu tìm nguyên nhân gốc rễ.</v>
       </c>
       <c r="E13" t="str">
+        <v>Phương pháp tính toán điểm ưu tiên RICE của Product Backlog — sắp xếp độ ưu tiên</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Quy trình viết kịch bản kiểm thử tự động Given-When-Then — thiết kế test case</v>
+      </c>
+      <c r="G13" t="str">
         <v>Phương pháp đặt câu hỏi 5 Why liên tiếp ở từng nhánh xương cá — tìm nguyên nhân gốc rễ đa chiều</v>
       </c>
-      <c r="F13" t="str">
+      <c r="H13" t="str">
         <v>Kỹ thuật ước lượng Story Point bằng Planning Poker trong sprint — ước lượng độ phức tạp</v>
       </c>
-      <c r="G13" t="str">
-        <v>Phương pháp tính toán điểm ưu tiên RICE của Product Backlog — sắp xếp độ ưu tiên</v>
-      </c>
-      <c r="H13" t="str">
-        <v>Quy trình viết kịch bản kiểm thử tự động Given-When-Then — thiết kế test case</v>
-      </c>
       <c r="I13">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -801,19 +801,19 @@
         <v>Value Proposition Canvas (VPC) đi sâu vào chi tiết của 2 ô này, giúp BA thiết kế sản phẩm khớp (fit) giữa Pain Relievers/Gain Creators của sản phẩm với Pains/Gains của phân khúc khách hàng.</v>
       </c>
       <c r="E14" t="str">
+        <v>Sơ đồ phân rã chức năng hệ thống (Functional Decomposition) — sơ đồ chức năng</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Biểu đồ luồng dữ liệu cấp 0 (Data Flow Diagram Level 0) — sơ đồ luồng dữ liệu</v>
+      </c>
+      <c r="G14" t="str">
         <v>Value Proposition Canvas (VPC) với sơ đồ Khớp (Fit) giữa Customer Profile và Value Map — bản đồ tuyên bố giá trị</v>
-      </c>
-      <c r="F14" t="str">
-        <v>Sơ đồ phân rã chức năng hệ thống (Functional Decomposition) — sơ đồ chức năng</v>
-      </c>
-      <c r="G14" t="str">
-        <v>Biểu đồ luồng dữ liệu cấp 0 (Data Flow Diagram Level 0) — sơ đồ luồng dữ liệu</v>
       </c>
       <c r="H14" t="str">
         <v>Mô hình phân tích chuỗi giá trị của Michael Porter (Value Chain) — sơ đồ chuỗi giá trị</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -830,19 +830,19 @@
         <v>Chiến lược S-O sử dụng những điểm mạnh bên trong để khai thác triệt để các cơ hội mở ra từ môi trường bên ngoài, tạo bước đột phá kinh doanh.</v>
       </c>
       <c r="E15" t="str">
+        <v>Bỏ qua hoàn toàn các điểm yếu nội bộ để tập trung mua lại các công ty đối thủ — thâu tóm thị trường</v>
+      </c>
+      <c r="F15" t="str">
         <v>Sử dụng chiến lược kết hợp S-O (Strengths - Opportunities) để phát huy tối đa lợi thế cạnh tranh — chiến lược tấn công</v>
       </c>
-      <c r="F15" t="str">
+      <c r="G15" t="str">
         <v>Sử dụng chiến lược kết hợp W-T (Weaknesses - Threats) để giảm thiểu rủi ro đóng cửa công ty — chiến lược phòng thủ</v>
-      </c>
-      <c r="G15" t="str">
-        <v>Bỏ qua hoàn toàn các điểm yếu nội bộ để tập trung mua lại các công ty đối thủ — thâu tóm thị trường</v>
       </c>
       <c r="H15" t="str">
         <v>Yêu cầu đội ngũ lập trình viên tự bỏ tiền túi ra mua thêm máy chủ Cloud mới — cắt giảm chi phí</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -862,13 +862,13 @@
         <v>Duy trì tính truy vết yêu cầu (Traceability), phê duyệt thay đổi (Change control) và sắp xếp độ ưu tiên yêu cầu — quản trị yêu cầu</v>
       </c>
       <c r="F16" t="str">
+        <v>Chạy thử nghiệm phần mềm thực tế với người dùng cuối ở giai đoạn UAT — kiểm thử nghiệm thu</v>
+      </c>
+      <c r="G16" t="str">
         <v>Tuyển dụng nhân sự và đào tạo kỹ năng lập trình cho các developer mới — quản lý nhân sự</v>
       </c>
-      <c r="G16" t="str">
+      <c r="H16" t="str">
         <v>Viết mã nguồn bằng ngôn ngữ TypeScript và triển khai lên môi trường AWS — triển khai kỹ thuật</v>
-      </c>
-      <c r="H16" t="str">
-        <v>Chạy thử nghiệm phần mềm thực tế với người dùng cuối ở giai đoạn UAT — kiểm thử nghiệm thu</v>
       </c>
       <c r="I16">
         <v>1</v>
@@ -888,19 +888,19 @@
         <v>Các nghị định, luật lệ mới ban hành từ chính phủ là các ràng buộc vĩ mô thuộc nhóm Legal (Pháp lý) hoặc Political (Chính trị) trong mô hình PESTEL.</v>
       </c>
       <c r="E17" t="str">
-        <v>Legal (Pháp lý) hoặc Political (Chính trị) — các quy định pháp luật và chính sách quản lý</v>
+        <v>Technological (Công nghệ) hoặc Economic (Kinh tế) — hạ tầng kỹ thuật và lạm phát tiền tệ</v>
       </c>
       <c r="F17" t="str">
         <v>Environmental (Môi trường) hoặc Social (Xã hội) — các yếu tố tự nhiên và xu hướng văn hóa</v>
       </c>
       <c r="G17" t="str">
-        <v>Technological (Công nghệ) hoặc Economic (Kinh tế) — hạ tầng kỹ thuật và lạm phát tiền tệ</v>
+        <v>Legal (Pháp lý) hoặc Political (Chính trị) — các quy định pháp luật và chính sách quản lý</v>
       </c>
       <c r="H17" t="str">
         <v>Nội tại điểm yếu (Weakness) của phần mềm ví điện tử đang phát triển — yếu tố nội bộ</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -920,13 +920,13 @@
         <v>Phân tích Cost-Benefit (Chi phí - Lợi ích) kết hợp ma trận ưu tiên yêu cầu theo mục tiêu chiến lược của doanh nghiệp — phân tích kinh tế định lượng</v>
       </c>
       <c r="F18" t="str">
+        <v>Chạy kịch bản test hiệu năng hệ thống bằng công cụ Apache JMeter — kiểm thử kỹ thuật</v>
+      </c>
+      <c r="G18" t="str">
         <v>Sơ đồ phân rã Use Case UML của hệ thống tổng đài tự động — phân tích ca sử dụng</v>
       </c>
-      <c r="G18" t="str">
+      <c r="H18" t="str">
         <v>Ma trận RACI để xác định xem ai là người có lương cao hơn để nghe theo ý kiến họ — dựa trên cấp bậc</v>
-      </c>
-      <c r="H18" t="str">
-        <v>Chạy kịch bản test hiệu năng hệ thống bằng công cụ Apache JMeter — kiểm thử kỹ thuật</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -946,19 +946,19 @@
         <v>Tính năng AI dự báo là dạng Attractive (nếu chạy tốt) hoặc Indifferent (nếu chạy không chính xác, khách hàng không quan tâm lắm). Vì nỗ lực lớn nhưng giá trị chưa rõ ràng, BA cần tư vấn PO không đưa vào MVP để bảo vệ scope.</v>
       </c>
       <c r="E19" t="str">
-        <v>Attractive (Hấp dẫn) hoặc Indifferent (Thờ ơ) — cần đánh giá kỹ lưỡng, có thể đưa vào backlog nghiên cứu (Spike) thay vì làm ngay làm tăng rủi ro dự án — cân đối giá trị</v>
+        <v>One-dimensional (Tuyến tính) — khách hàng sẽ đánh giá chất lượng sản phẩm tăng dần theo số lượng thuật toán AI được code — tuyến tính hài lòng</v>
       </c>
       <c r="F19" t="str">
         <v>Must-be (Cơ bản) — bắt buộc phải phát triển ngay từ bản MVP đầu tiên để hệ thống hoạt động được — yêu cầu cốt lõi</v>
       </c>
       <c r="G19" t="str">
-        <v>One-dimensional (Tuyến tính) — khách hàng sẽ đánh giá chất lượng sản phẩm tăng dần theo số lượng thuật toán AI được code — tuyến tính hài lòng</v>
+        <v>Attractive (Hấp dẫn) hoặc Indifferent (Thờ ơ) — cần đánh giá kỹ lưỡng, có thể đưa vào backlog nghiên cứu (Spike) thay vì làm ngay làm tăng rủi ro dự án — cân đối giá trị</v>
       </c>
       <c r="H19" t="str">
         <v>Reverse (Ngược chiều) — tính năng này sẽ làm khách hàng cực kỳ ghét sản phẩm nếu hệ thống hoạt động chính xác — tác động tiêu cực</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -978,13 +978,13 @@
         <v>Hoạt động hỗ trợ (Support Activities); đóng vai trò tối ưu hóa hiệu suất và giảm chi phí cho các hoạt động chính thông qua ứng dụng công nghệ thông tin — nâng cao năng lực nội tại</v>
       </c>
       <c r="F20" t="str">
-        <v>Hoạt động chính (Primary Activities); trực tiếp tham gia vào việc sản xuất và vận chuyển sản phẩm vật lý đến tay khách hàng — tạo ra sản phẩm</v>
+        <v>Hoạt động tiếp thị trực tuyến; chạy quảng cáo trên các nền tảng mạng xã hội lớn — thu hút khách hàng</v>
       </c>
       <c r="G20" t="str">
         <v>Hoạt động quản trị rủi ro pháp lý; ngăn chặn các cuộc tấn công bảo mật từ hacker bên ngoài — bảo mật hệ thống</v>
       </c>
       <c r="H20" t="str">
-        <v>Hoạt động tiếp thị trực tuyến; chạy quảng cáo trên các nền tảng mạng xã hội lớn — thu hút khách hàng</v>
+        <v>Hoạt động chính (Primary Activities); trực tiếp tham gia vào việc sản xuất và vận chuyển sản phẩm vật lý đến tay khách hàng — tạo ra sản phẩm</v>
       </c>
       <c r="I20">
         <v>1</v>
@@ -1004,19 +1004,19 @@
         <v>Nhóm High Power/Low Interest (ví dụ: Giám đốc tài chính hoặc Trưởng bộ phận an ninh thông tin) có quyền phủ quyết dự án. Nếu làm phiền họ quá nhiều bằng chi tiết nhỏ (Manage Closely) họ sẽ bực mình, nhưng nếu không giữ họ hài lòng (Keep Satisfied), họ có thể block dự án khi phát sinh vấn đề liên quan đến họ.</v>
       </c>
       <c r="E21" t="str">
-        <v>Keep Satisfied (Giữ cho họ hài lòng) bằng cách báo cáo các mốc tiến độ lớn một cách ngắn gọn, súc tích và tham vấn họ ở các quyết định quan trọng ảnh hưởng đến quyền lợi của họ — quản lý kỳ vọng khôn ngoan</v>
+        <v>Manage Closely (Quản lý chặt chẽ) bằng cách gửi email báo cáo chi tiết hàng ngày và bắt họ tham gia tất cả các cuộc họp Daily Scrum — làm phiền không cần thiết</v>
       </c>
       <c r="F21" t="str">
         <v>Monitor (Theo dõi sát sao) nhưng không cần cung cấp bất kỳ thông tin nào để tránh làm phiền họ — theo dõi thụ động</v>
       </c>
       <c r="G21" t="str">
-        <v>Manage Closely (Quản lý chặt chẽ) bằng cách gửi email báo cáo chi tiết hàng ngày và bắt họ tham gia tất cả các cuộc họp Daily Scrum — làm phiền không cần thiết</v>
+        <v>Bỏ qua hoàn toàn vì họ không quan tâm trực tiếp đến dự án nên sẽ không gây ảnh hưởng gì — chủ quan nguy hiểm</v>
       </c>
       <c r="H21" t="str">
-        <v>Bỏ qua hoàn toàn vì họ không quan tâm trực tiếp đến dự án nên sẽ không gây ảnh hưởng gì — chủ quan nguy hiểm</v>
+        <v>Keep Satisfied (Giữ cho họ hài lòng) bằng cách báo cáo các mốc tiến độ lớn một cách ngắn gọn, súc tích và tham vấn họ ở các quyết định quan trọng ảnh hưởng đến quyền lợi của họ — quản lý kỳ vọng khôn ngoan</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -1039,10 +1039,10 @@
         <v>Chọn lựa ngôn ngữ lập trình Java hay C# để viết API kết nối dữ liệu giữa các cửa hàng — lựa chọn công nghệ</v>
       </c>
       <c r="G22" t="str">
+        <v>Tìm kiếm nhà cung cấp máy chủ vật lý có giá thuê rẻ nhất trên thị trường — tối ưu chi phí phần cứng</v>
+      </c>
+      <c r="H22" t="str">
         <v>Tính toán số lượng nhân viên bán hàng tối đa cần tuyển dụng cho mỗi cửa hàng vật lý — quản lý nhân sự cửa hàng</v>
-      </c>
-      <c r="H22" t="str">
-        <v>Tìm kiếm nhà cung cấp máy chủ vật lý có giá thuê rẻ nhất trên thị trường — tối ưu chi phí phần cứng</v>
       </c>
       <c r="I22">
         <v>1</v>
@@ -1065,13 +1065,13 @@
         <v>Phân tích trạng thái hiện tại, xác định trạng thái tương lai mong muốn, đánh giá rủi ro chiến lược và xác định phương án thay đổi (Change Strategy) — xác định lộ trình chuyển đổi</v>
       </c>
       <c r="F23" t="str">
+        <v>Thiết kế kiến trúc cơ sở dữ liệu vật lý và cài đặt hệ quản trị cơ sở dữ liệu PostgreSQL — thiết kế database</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Thương lượng mức giá chiết khấu phần trăm với nhà cung cấp dịch vụ máy chủ Cloud — thương thảo chi phí</v>
+      </c>
+      <c r="H23" t="str">
         <v>Viết toàn bộ kịch bản kiểm thử tích hợp API và chạy tự động trên môi trường Jenkins — kiểm thử tự động</v>
-      </c>
-      <c r="G23" t="str">
-        <v>Thiết kế kiến trúc cơ sở dữ liệu vật lý và cài đặt hệ quản trị cơ sở dữ liệu PostgreSQL — thiết kế database</v>
-      </c>
-      <c r="H23" t="str">
-        <v>Thương lượng mức giá chiết khấu phần trăm với nhà cung cấp dịch vụ máy chủ Cloud — thương thảo chi phí</v>
       </c>
       <c r="I23">
         <v>1</v>
@@ -1094,13 +1094,13 @@
         <v>Vì nó làm rõ ai là người chịu trách nhiệm giải trình cuối cùng (Accountable - chỉ có 1 người duy nhất), tránh tình trạng đùn đẩy trách nhiệm hoặc có quá nhiều người cùng đòi quyết định — phân định thẩm quyền rõ ràng</v>
       </c>
       <c r="F24" t="str">
-        <v>Vì RACI tự động hóa quy trình ký duyệt tài liệu điện tử thông qua các thuật toán mã hóa Blockchain — tự động hóa chữ ký</v>
+        <v>Vì nó loại bỏ hoàn toàn vai trò của giám đốc dự án ra khỏi quy trình kiểm soát tiến độ công việc — loại bỏ PM</v>
       </c>
       <c r="G24" t="str">
         <v>Vì nó bắt buộc tất cả các lập trình viên phải ký cam kết không được viết code sai so với đặc tả của BA — giảm thiểu bug code</v>
       </c>
       <c r="H24" t="str">
-        <v>Vì nó loại bỏ hoàn toàn vai trò của giám đốc dự án ra khỏi quy trình kiểm soát tiến độ công việc — loại bỏ PM</v>
+        <v>Vì RACI tự động hóa quy trình ký duyệt tài liệu điện tử thông qua các thuật toán mã hóa Blockchain — tự động hóa chữ ký</v>
       </c>
       <c r="I24">
         <v>1</v>
@@ -1123,13 +1123,13 @@
         <v>Dùng để thấu hiểu quan điểm của các bên liên quan về một hệ thống phức tạp; viết tắt của Customers, Actors, Transformation process, World view, Owners, Environmental constraints — phân tích góc nhìn hệ thống</v>
       </c>
       <c r="F25" t="str">
-        <v>Dùng để tính toán hiệu năng của hệ quản trị cơ sở dữ liệu quan hệ; viết tắt của Cache, Allocation, Transactions, Write-speed, Operations, Execution — chỉ số cơ sở dữ liệu</v>
+        <v>Dùng để lập lịch trình họp hàng tuần cho Scrum Team; viết tắt của Calendar, Agenda, Timebox, Weekly-goals, Outcomes, Evaluation — tổ chức cuộc họp</v>
       </c>
       <c r="G25" t="str">
         <v>Dùng để thiết kế giao diện đồ họa cho ứng dụng di động; viết tắt của Colors, Alignments, Typography, Width, Objects, Effects — quy tắc thiết kế giao diện</v>
       </c>
       <c r="H25" t="str">
-        <v>Dùng để lập lịch trình họp hàng tuần cho Scrum Team; viết tắt của Calendar, Agenda, Timebox, Weekly-goals, Outcomes, Evaluation — tổ chức cuộc họp</v>
+        <v>Dùng để tính toán hiệu năng của hệ quản trị cơ sở dữ liệu quan hệ; viết tắt của Cache, Allocation, Transactions, Write-speed, Operations, Execution — chỉ số cơ sở dữ liệu</v>
       </c>
       <c r="I25">
         <v>1</v>
@@ -1152,13 +1152,13 @@
         <v>Legal (Pháp lý); buộc thiết kế hệ thống phải có bước duyệt thủ công (Human-in-the-loop) đối với các hồ sơ bị AI đánh giá từ chối — ràng buộc pháp lý bắt buộc</v>
       </c>
       <c r="F26" t="str">
+        <v>Technological (Công nghệ); yêu cầu hệ thống phải sử dụng thuật toán học máy Deep Learning thay vì Random Forest — lựa chọn thuật toán</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Economic (Kinh tế); yêu cầu hệ thống phải tính phí giao dịch cao hơn đối với các hồ sơ bảo hiểm trực tuyến — điều chỉnh phí</v>
+      </c>
+      <c r="H26" t="str">
         <v>Social (Xã hội); yêu cầu hệ thống phải đổi giao diện sang màu vàng để tạo cảm giác thân thiện với người dùng — thiết kế thân thiện</v>
-      </c>
-      <c r="G26" t="str">
-        <v>Technological (Công nghệ); yêu cầu hệ thống phải sử dụng thuật toán học máy Deep Learning thay vì Random Forest — lựa chọn thuật toán</v>
-      </c>
-      <c r="H26" t="str">
-        <v>Economic (Kinh tế); yêu cầu hệ thống phải tính phí giao dịch cao hơn đối với các hồ sơ bảo hiểm trực tuyến — điều chỉnh phí</v>
       </c>
       <c r="I26">
         <v>1</v>
